--- a/DOC/State.xlsx
+++ b/DOC/State.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamed\OneDrive\Documents\GitHub\ChangeOver\DOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{947F0E53-9167-4D4E-A419-0D8554770EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CFDC40-DE6D-4B52-89E5-33D0ABC7ABCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E560ED72-D2D6-4705-8BD3-D811E2932B85}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E560ED72-D2D6-4705-8BD3-D811E2932B85}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT_OUTPUT" sheetId="1" r:id="rId1"/>
+    <sheet name="UI" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="52">
   <si>
     <t>21~28</t>
   </si>
@@ -64,13 +65,145 @@
   </si>
   <si>
     <t>سوئیچ بین باتری یا ورودی</t>
+  </si>
+  <si>
+    <t>INPUTS</t>
+  </si>
+  <si>
+    <t>OUTPUTS</t>
+  </si>
+  <si>
+    <t>چراغ سبز دائم روشن</t>
+  </si>
+  <si>
+    <t>حالت</t>
+  </si>
+  <si>
+    <t>LED G</t>
+  </si>
+  <si>
+    <t>LED R</t>
+  </si>
+  <si>
+    <t>LED Y</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>INPUT_OK</t>
+  </si>
+  <si>
+    <t>شرح</t>
+  </si>
+  <si>
+    <t>OUTPUT VOLTAE</t>
+  </si>
+  <si>
+    <t>INPUT VOLTAGE</t>
+  </si>
+  <si>
+    <t>CHARGING</t>
+  </si>
+  <si>
+    <t>22~28</t>
+  </si>
+  <si>
+    <t>Histersis_Battery</t>
+  </si>
+  <si>
+    <t>IN&lt;21</t>
+  </si>
+  <si>
+    <t>USE_BATTERY_1</t>
+  </si>
+  <si>
+    <t>USE_BATTERY_2</t>
+  </si>
+  <si>
+    <t>BATT&lt;28</t>
+  </si>
+  <si>
+    <t>24 &lt; BAT &lt; 28</t>
+  </si>
+  <si>
+    <t>22 &lt; BAT &lt; 24</t>
+  </si>
+  <si>
+    <t>USE_BATTERY_3</t>
+  </si>
+  <si>
+    <t>21 &lt; BAT &lt; 22</t>
+  </si>
+  <si>
+    <t>USE_BATTERY_4</t>
+  </si>
+  <si>
+    <t>BATTERY VOLTAGE</t>
+  </si>
+  <si>
+    <t>BAT &lt; 21</t>
+  </si>
+  <si>
+    <t>BUZZER</t>
+  </si>
+  <si>
+    <t>در این حالت چراغ سبز هر 10ثانیه یک چشمک با طول 100 میلی ثانیه میزند.
+فقط یکبار یک بوق ممتد 5ثانیه ای میزند.</t>
+  </si>
+  <si>
+    <t>چراغ سبز دائم روشن + چراغ زرد نسبت به مقدار شارژ چشمک میزند(باتری خالی چراغ زد دائم روشن و باتری پر چراغ زرد خاموش).
+با رسیدن ولتاژباتری به ((باتری-هیسترزیس)) عملیات شارژ شروع میشود و با رسیدن ولتاژ باتری به 28 ولت قطع می شود.</t>
+  </si>
+  <si>
+    <t>در این حالت چراغ سبز به نسبت درصد پر بودن باتری  هر یک ثانیه چشمک میزند.(باتری پر دائم روشن و باتری خالی 100 میلی ثانیه در هر 10 ثانیه)
+همزمان هر 60 ثانیه دو بوق میزند با فاصله زمانی 0.5 ثانیه.</t>
+  </si>
+  <si>
+    <t>در این حالت چراغ سبز به نسبت درصد پر بودن باتری هر یک ثانیه چشمک میزند.(باتری پر دائم روشن و باتری خالی 100 میلی ثانیه در هر 10 ثانیه)
+همزمان هر 600 ثانیه یک بوق میزند.</t>
+  </si>
+  <si>
+    <t>در این حالت فقط چراغ سبز به نسبت درصد پر بودن باتری چشمک میزند(باتری پر دائم روشن و باتری خالی 100 میلی ثانیه در هر 10 ثانیه).</t>
+  </si>
+  <si>
+    <t>ERROR_HIGH_VOLTAGE</t>
+  </si>
+  <si>
+    <t>IN&gt;28</t>
+  </si>
+  <si>
+    <t>در این حالت چراغ قرمز چشمک میزند(هر 1 ثانیه با دیوتی 50درصد)
+همزمان بوق هم در ثانیه با دیوتی 50 درصد به صدا در میآید</t>
+  </si>
+  <si>
+    <t>Histersis_Input</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>charging majol</t>
+  </si>
+  <si>
+    <t>STATEGIES</t>
+  </si>
+  <si>
+    <t>out zero
+changeover majol</t>
+  </si>
+  <si>
+    <t>fail majol</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,16 +211,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Vazirmatn"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Vazirmatn"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Vazirmatn"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Vazirmatn"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -95,17 +257,107 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -415,75 +667,752 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7AB0D5-D7FF-447D-8F9C-50343D8EAA21}">
-  <dimension ref="A2:D7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="24.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="1" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row r="4" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="C6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>1</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B7" s="2" t="str">
         <f>B3</f>
         <v>21~28</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:D5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94FE7CA8-C6AD-47FD-8291-061B2A552A4C}">
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="18.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="60.75" style="11" customWidth="1"/>
+    <col min="9" max="12" width="9" style="8"/>
+    <col min="13" max="13" width="15" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f>C3</f>
+        <v>21~28</v>
+      </c>
+      <c r="E3" s="2">
+        <v>28</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="84" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f>C4</f>
+        <v>22~28</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="42" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f>E5</f>
+        <v>24 &lt; BAT &lt; 28</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="63" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f>E6</f>
+        <v>22 &lt; BAT &lt; 24</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="63" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f>E7</f>
+        <v>21 &lt; BAT &lt; 22</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="63" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="42" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <f>C9</f>
+        <v>IN&gt;28</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="I3:I26">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J28">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K26">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L26">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DOC/State.xlsx
+++ b/DOC/State.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamed\OneDrive\Documents\GitHub\ChangeOver\DOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CFDC40-DE6D-4B52-89E5-33D0ABC7ABCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBB100A-3F4D-4189-BD2B-D6D451CE2368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E560ED72-D2D6-4705-8BD3-D811E2932B85}"/>
   </bookViews>
@@ -176,10 +176,6 @@
     <t>IN&gt;28</t>
   </si>
   <si>
-    <t>در این حالت چراغ قرمز چشمک میزند(هر 1 ثانیه با دیوتی 50درصد)
-همزمان بوق هم در ثانیه با دیوتی 50 درصد به صدا در میآید</t>
-  </si>
-  <si>
     <t>Histersis_Input</t>
   </si>
   <si>
@@ -197,6 +193,10 @@
   </si>
   <si>
     <t>fail majol</t>
+  </si>
+  <si>
+    <t>در این حالت چراغ قرمز چشمک میزند(هر 1 ثانیه با دیوتی 50درصد)
+همزمان بوق هم هر یک ثانیه با دیوتی 50 درصد.</t>
   </si>
 </sst>
 </file>
@@ -819,7 +819,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>20</v>
@@ -837,7 +837,7 @@
         <v>37</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -879,7 +879,7 @@
         <v>18</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="84" x14ac:dyDescent="0.2">
@@ -921,7 +921,7 @@
         <v>18</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="42" x14ac:dyDescent="0.2">
@@ -963,7 +963,7 @@
         <v>18</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="63" x14ac:dyDescent="0.2">
@@ -1005,7 +1005,7 @@
         <v>17</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="63" x14ac:dyDescent="0.2">
@@ -1047,7 +1047,7 @@
         <v>17</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="63" x14ac:dyDescent="0.2">
@@ -1088,7 +1088,7 @@
         <v>17</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="42" x14ac:dyDescent="0.2">
@@ -1115,7 +1115,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>18</v>
@@ -1130,7 +1130,7 @@
         <v>17</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
